--- a/literature-review/results/results_topic1.xlsx
+++ b/literature-review/results/results_topic1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\177020724\Documents\Studium\Thesis\Literature Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22BE67A8-326C-4C1D-A07B-90196770DD4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01ABAB40-B697-4F24-B87D-54F9C16F039D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-192" yWindow="-192" windowWidth="41664" windowHeight="16944" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="188">
   <si>
     <t>Geoengine: A platform for production-ready geospatial research</t>
   </si>
@@ -95,9 +95,6 @@
   </si>
   <si>
     <t>Processing</t>
-  </si>
-  <si>
-    <t>Deployment</t>
   </si>
   <si>
     <t>Datasource</t>
@@ -191,9 +188,6 @@
     <t>Amazon S3</t>
   </si>
   <si>
-    <t>Training Framework</t>
-  </si>
-  <si>
     <t>Multi-path data fusion methodology (processing of differnet modalities), Masking</t>
   </si>
   <si>
@@ -387,9 +381,6 @@
     <t>Prefect Core</t>
   </si>
   <si>
-    <t>Confusion matrix</t>
-  </si>
-  <si>
     <t>Sentinel, ASTER</t>
   </si>
   <si>
@@ -1299,6 +1290,591 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t>Apache Airflow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> on kubernetes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Logging in a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Prometheus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> database</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Grafana</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TensorBoard</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TensorFlow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PyTorch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,  U-Net with EfficientNet-B0 backbone</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Apache Airflow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (based on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Kubernetes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>JupyterHub</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Dask</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HPC Kubernetes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cluster</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Kubernetes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based monitoring</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Dask</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cluster (based on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Kubernetes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Amazon S3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>relational database</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> MLflow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> as a model registry</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cloud object store</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (not further defined)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Relational database</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (not further defined)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Apache Airflow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (based on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Kubernetes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Seldon Core</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Automated testing in a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GitHub Actions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> CI/CD pipeline using a test dataset</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Metrics tracking using </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Seldon Core</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Prometheus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Prefect Core</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, storing SHA reference to model version in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GitHub repo</t>
+    </r>
+  </si>
+  <si>
+    <t>Cloud Deployment</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Container orchestration on AWS for deep learning workloads. Orchestration using </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AWS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Amazon Web Services (AWS)</t>
     </r>
     <r>
@@ -1309,572 +1885,53 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> using </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CloudFormation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and the managed </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Elastic
-Kubernetes Service (EKS)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Apache Airflow</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> on kubernetes</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Logging in a </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Prometheus</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> database</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Grafana</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>TensorBoard</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>TensorFlow</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PyTorch</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>,  U-Net with EfficientNet-B0 backbone</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Apache Airflow</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (based on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Kubernetes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">), </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>JupyterHub</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Dask</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>HPC Kubernetes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> cluster</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Kubernetes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based monitoring</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Dask</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> cluster (based on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Kubernetes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Amazon S3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>relational database</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> MLflow</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> as a model registry</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Cloud object store</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (not further defined)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Relational database</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (not further defined)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Apache Airflow</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (based on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Kubernetes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">), </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Seldon Core</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Automated testing in a </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>GitHub Actions</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> CI/CD pipeline using a test dataset</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Metrics tracking using </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Seldon Core</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Prometheus</t>
+      <t xml:space="preserve"> using CloudFormation and the managed Elastic
+Kubernetes Service (EKS). </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud deployment (not further specified) </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mentions </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MEOW-ML</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for logging/monitoring</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Image storage in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AWS S3</t>
     </r>
     <r>
       <rPr>
@@ -1888,38 +1945,58 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Prefect Core</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, storing SHA reference to model version in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>GitHub repo</t>
-    </r>
+    <t xml:space="preserve">Training </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Automated training using the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Phobos </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">library </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Training managed via </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hopsworks</t>
+    </r>
+  </si>
+  <si>
+    <t>Automated training and re-training of models mentioned</t>
+  </si>
+  <si>
+    <t>Transformed (self-annotated) dataset is saved for further use</t>
+  </si>
+  <si>
+    <t>Describes serving in tradational backend-API-frontend architecture</t>
   </si>
 </sst>
 </file>
@@ -2236,9 +2313,9 @@
     <tableColumn id="9" xr3:uid="{A0269DFD-75FF-4940-BECA-F67DBB4D17D4}" name="Robustness testing" dataDxfId="16"/>
     <tableColumn id="10" xr3:uid="{232E9CE2-4916-4233-BC07-E3E4A3A081B3}" name="Serving" dataDxfId="15"/>
     <tableColumn id="11" xr3:uid="{5AA90D9C-1033-4A82-BC03-B93164FCC4C1}" name="Processing" dataDxfId="14"/>
-    <tableColumn id="12" xr3:uid="{20BC529F-0800-446A-8F47-AC38727C0449}" name="Deployment" dataDxfId="13"/>
+    <tableColumn id="12" xr3:uid="{20BC529F-0800-446A-8F47-AC38727C0449}" name="Cloud Deployment" dataDxfId="13"/>
     <tableColumn id="13" xr3:uid="{420767DF-8F51-47D1-A265-155E164F3FB4}" name="Datasource" dataDxfId="12"/>
-    <tableColumn id="14" xr3:uid="{EA8AFE10-39EB-4529-8923-318C529A0A0C}" name="Training Framework" dataDxfId="11"/>
+    <tableColumn id="14" xr3:uid="{EA8AFE10-39EB-4529-8923-318C529A0A0C}" name="Training " dataDxfId="11"/>
     <tableColumn id="15" xr3:uid="{6A527EF1-5F9E-4EDF-B4A8-E7F94C1E1582}" name="Prediction/Inference" dataDxfId="10"/>
     <tableColumn id="16" xr3:uid="{22499623-8F36-4FA8-BDEA-B296E884F24D}" name="Reporting" dataDxfId="9"/>
     <tableColumn id="17" xr3:uid="{777C05CE-3755-41E8-A9E6-0106D49CE8E2}" name="Testing" dataDxfId="8"/>
@@ -2543,42 +2620,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="31.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="31.1015625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" customWidth="1"/>
-    <col min="4" max="4" width="6.5546875" style="20" customWidth="1"/>
-    <col min="5" max="5" width="29.109375" customWidth="1"/>
-    <col min="6" max="6" width="28.5546875" customWidth="1"/>
-    <col min="7" max="7" width="22.77734375" customWidth="1"/>
-    <col min="8" max="8" width="19.21875" customWidth="1"/>
+    <col min="3" max="3" width="23.3125" customWidth="1"/>
+    <col min="4" max="4" width="6.5234375" style="20" customWidth="1"/>
+    <col min="5" max="5" width="29.1015625" customWidth="1"/>
+    <col min="6" max="6" width="28.5234375" customWidth="1"/>
+    <col min="7" max="7" width="22.7890625" customWidth="1"/>
+    <col min="8" max="8" width="19.20703125" customWidth="1"/>
     <col min="9" max="9" width="25" customWidth="1"/>
-    <col min="10" max="23" width="20.5546875" customWidth="1"/>
-    <col min="24" max="24" width="36.77734375" customWidth="1"/>
+    <col min="10" max="23" width="20.5234375" customWidth="1"/>
+    <col min="24" max="24" width="36.7890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:25" ht="18.3" x14ac:dyDescent="0.7">
       <c r="A1" s="12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="M1" s="1"/>
       <c r="X1" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="Y1" s="14"/>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3" t="s">
         <v>16</v>
       </c>
@@ -2589,10 +2666,10 @@
         <v>18</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>21</v>
@@ -2601,10 +2678,10 @@
         <v>20</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>23</v>
@@ -2613,49 +2690,49 @@
         <v>24</v>
       </c>
       <c r="L2" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="N2" s="3" t="s">
-        <v>56</v>
+        <v>182</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="S2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y2" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="T2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="W2" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="X2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="Y2" s="4" t="s">
-        <v>43</v>
-      </c>
     </row>
-    <row r="3" spans="1:25" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2">
         <v>0</v>
       </c>
@@ -2669,68 +2746,68 @@
         <v>2022</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J3" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="O3" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="P3" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="L3" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="M3" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="N3" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="O3" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>145</v>
-      </c>
       <c r="R3" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="T3" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="U3" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="V3" s="15" t="s">
-        <v>107</v>
+        <v>181</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="X3" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="Y3" s="5"/>
     </row>
-    <row r="4" spans="1:25" ht="72" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -2744,68 +2821,68 @@
         <v>2022</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="P4" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F4" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="K4" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="L4" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="M4" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="N4" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="P4" s="3" t="s">
+      <c r="Q4" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="Q4" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="R4" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="S4" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="W4" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="X4" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="Y4" s="5"/>
     </row>
-    <row r="5" spans="1:25" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -2819,68 +2896,68 @@
         <v>2021</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="K5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="L5" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="M5" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="O5" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="P5" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q5" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="S5" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="T5" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="W5" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="X5" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="L5" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="M5" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="O5" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="P5" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q5" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="S5" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="T5" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="W5" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="X5" s="5" t="s">
-        <v>73</v>
       </c>
       <c r="Y5" s="5"/>
     </row>
-    <row r="6" spans="1:25" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2">
         <v>3</v>
       </c>
@@ -2894,68 +2971,68 @@
         <v>2022</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="J6" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="L6" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="P6" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q6" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="R6" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="S6" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="T6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="U6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="V6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="W6" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="X6" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="L6" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="P6" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q6" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="R6" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="S6" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="T6" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="U6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="V6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="W6" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="X6" s="5" t="s">
-        <v>65</v>
       </c>
       <c r="Y6" s="5"/>
     </row>
-    <row r="7" spans="1:25" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -2969,68 +3046,68 @@
         <v>2024</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J7" s="16" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="O7" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="P7" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="R7" s="15" t="s">
-        <v>107</v>
+        <v>180</v>
       </c>
       <c r="S7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="T7" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="U7" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="V7" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="W7" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="X7" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="T7" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="U7" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="V7" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="W7" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="X7" s="5" t="s">
-        <v>60</v>
       </c>
       <c r="Y7" s="5"/>
     </row>
-    <row r="8" spans="1:25" ht="72" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -3044,7 +3121,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>19</v>
@@ -3053,59 +3130,59 @@
         <v>22</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="M8" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="P8" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q8" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="R8" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="S8" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="T8" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="U8" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="V8" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="W8" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="X8" s="5" t="s">
         <v>126</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="P8" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q8" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="R8" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="S8" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="T8" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="U8" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="V8" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="W8" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="X8" s="5" t="s">
-        <v>129</v>
       </c>
       <c r="Y8" s="5"/>
     </row>
-    <row r="9" spans="1:25" ht="72" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -3119,70 +3196,70 @@
         <v>2024</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="M9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="I9" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="J9" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="N9" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O9" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="P9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q9" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="R9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="Q9" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="R9" s="2" t="s">
+      <c r="S9" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="T9" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="U9" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="W9" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="X9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="S9" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="T9" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="U9" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="V9" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="W9" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="X9" s="5" t="s">
-        <v>40</v>
-      </c>
       <c r="Y9" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -3196,446 +3273,446 @@
         <v>2023</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="N10" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="O10" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="P10" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="R10" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="S10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H10" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="I10" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="N10" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="O10" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="P10" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="R10" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="T10" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W10" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="X10" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="Y10" s="5"/>
     </row>
-    <row r="11" spans="1:25" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" s="7" customFormat="1" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2">
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D11" s="22">
         <v>2023</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="J11" s="16" t="s">
-        <v>107</v>
+        <v>105</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>187</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="O11" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="P11" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q11" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="R11" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="T11" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="U11" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="V11" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="W11" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="X11" s="5" t="s">
         <v>92</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="O11" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="P11" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q11" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="R11" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="T11" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="U11" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="V11" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="W11" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="X11" s="5" t="s">
-        <v>94</v>
       </c>
       <c r="Y11" s="5"/>
     </row>
-    <row r="12" spans="1:25" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2">
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D12" s="15">
         <v>2023</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="M12" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="O12" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="S12" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="T12" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W12" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="X12" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Y12" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:25" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" s="2" customFormat="1" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2">
         <v>10</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D13" s="22">
         <v>2024</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H13" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="O13" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="P13" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q13" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="S13" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="T13" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="U13" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="W13" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="X13" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y13" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="I13" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="L13" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="O13" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="P13" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q13" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="S13" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="T13" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="U13" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="V13" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="W13" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="X13" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="Y13" s="5" t="s">
-        <v>112</v>
-      </c>
     </row>
-    <row r="14" spans="1:25" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2">
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D14" s="15">
         <v>2023</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F14" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="L14" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="G14" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="H14" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="I14" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="J14" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="K14" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="M14" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="N14" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="O14" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="P14" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="Q14" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="R14" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="S14" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="W14" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="X14" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="Y14" s="5"/>
     </row>
-    <row r="15" spans="1:25" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" s="2" customFormat="1" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2">
         <v>12</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D15" s="22">
         <v>2024</v>
       </c>
       <c r="E15" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="M15" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G15" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="H15" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="I15" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="L15" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="M15" s="2" t="s">
+      <c r="N15" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="O15" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="P15" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="S15" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="X15" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="N15" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="O15" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="S15" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="U15" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="V15" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="W15" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="X15" s="5" t="s">
-        <v>124</v>
-      </c>
       <c r="Y15" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
